--- a/jogos_2024-11-20.xlsx
+++ b/jogos_2024-11-20.xlsx
@@ -772,25 +772,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -798,43 +798,43 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.44</v>
+        <v>3.1</v>
       </c>
       <c r="M3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O3" t="n">
         <v>3.6</v>
       </c>
-      <c r="N3" t="n">
-        <v>7</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.95</v>
-      </c>
       <c r="P3" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.5</v>
+        <v>2.75</v>
       </c>
       <c r="R3" t="n">
         <v>1.36</v>
       </c>
       <c r="S3" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="T3" t="n">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="U3" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="V3" t="n">
         <v>1.05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="X3" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Y3" t="n">
         <v>1.95</v>
@@ -843,38 +843,38 @@
         <v>1.85</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>['69']</t>
+          <t>['58']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['16', '36', '43', '45+4']</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.05</v>
+        <v>1.59</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.48</v>
+        <v>1.26</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="AJ3" t="n">
-        <v>4.5</v>
+        <v>1.73</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45616.33333333334</v>
@@ -901,25 +901,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -927,43 +927,43 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.1</v>
+        <v>1.44</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="N4" t="n">
-        <v>2.1</v>
+        <v>7</v>
       </c>
       <c r="O4" t="n">
-        <v>3.6</v>
+        <v>1.95</v>
       </c>
       <c r="P4" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.75</v>
+        <v>6.5</v>
       </c>
       <c r="R4" t="n">
         <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="T4" t="n">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="U4" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="V4" t="n">
         <v>1.05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="X4" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Y4" t="n">
         <v>1.95</v>
@@ -972,38 +972,38 @@
         <v>1.85</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>['58']</t>
+          <t>['69']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>['16', '36', '43', '45+4']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.59</v>
+        <v>1.05</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.26</v>
+        <v>2.48</v>
       </c>
       <c r="AI4" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.73</v>
+        <v>4.5</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45616.33333333334</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,22 +1675,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="M10" t="n">
         <v>2.9</v>
       </c>
       <c r="N10" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="O10" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="P10" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="Q10" t="n">
         <v>4.33</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W10" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="X10" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="Y10" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>['45', '79']</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>['83']</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>2.55</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>2.75</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45616.66666666666</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,22 +2062,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="M13" t="n">
         <v>2.9</v>
       </c>
       <c r="N13" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="O13" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="P13" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="Q13" t="n">
         <v>4.33</v>
       </c>
       <c r="R13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="X13" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['45', '79']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>['83']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45616.66666666666</v>
@@ -2181,32 +2181,32 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hércules CF</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2217,28 +2217,28 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="M14" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
         <v>3.6</v>
       </c>
       <c r="O14" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="P14" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
         <v>4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="T14" t="n">
         <v>3.4</v>
@@ -2250,47 +2250,47 @@
         <v>1.07</v>
       </c>
       <c r="W14" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="X14" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.59</v>
+        <v>2.1</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>['38', '63']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>['61']</t>
+          <t>['67']</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AJ14" t="n">
         <v>2.5</v>
@@ -2449,22 +2449,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N16" t="n">
+        <v>6</v>
+      </c>
+      <c r="O16" t="n">
         <v>2.1</v>
       </c>
-      <c r="M16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N16" t="n">
+      <c r="P16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>6</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>['45+4', '65']</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AJ16" t="n">
         <v>3.6</v>
-      </c>
-      <c r="O16" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>4</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X16" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>['67']</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>2.5</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45616.6875</v>
@@ -2568,29 +2568,29 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Hércules CF</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>2</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.55</v>
+        <v>2.05</v>
       </c>
       <c r="M17" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="N17" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="O17" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="P17" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="Q17" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="S17" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="T17" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="U17" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="V17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="W17" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="X17" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="Y17" t="n">
-        <v>2</v>
+        <v>2.59</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.88</v>
+        <v>1.44</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AC17" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['45+4', '65']</t>
+          <t>['38', '63']</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['61']</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.4</v>
+        <v>1.62</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="AJ17" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45616.6875</v>
@@ -3481,25 +3481,25 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Vélez Sarsfield</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Lanús</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="M24" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="N24" t="n">
-        <v>4.5</v>
+        <v>5.75</v>
       </c>
       <c r="O24" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="P24" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="R24" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="S24" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="T24" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="U24" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="V24" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="W24" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="X24" t="n">
-        <v>2.65</v>
+        <v>3.04</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.7</v>
+        <v>2.08</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AA24" t="n">
-        <v>4.65</v>
+        <v>3.92</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>['29']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>['43']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AH24" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AJ24" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45616.80208333334</v>
@@ -3610,25 +3610,25 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vélez Sarsfield</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lanús</t>
+          <t>Rosario Central</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="M25" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="N25" t="n">
-        <v>5.75</v>
+        <v>4.5</v>
       </c>
       <c r="O25" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="P25" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="Q25" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="R25" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Z25" t="n">
         <v>1.44</v>
       </c>
-      <c r="S25" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X25" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AA25" t="n">
-        <v>3.92</v>
+        <v>4.65</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['29']</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['43']</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AJ25" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45616.80208333334</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,22 +3739,22 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Unión Santa Fe</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N26" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="O26" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>5</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T26" t="n">
         <v>3.4</v>
       </c>
-      <c r="M26" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N26" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="O26" t="n">
-        <v>4</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>3</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3.25</v>
-      </c>
       <c r="U26" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V26" t="n">
         <v>1.06</v>
       </c>
       <c r="W26" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="X26" t="n">
-        <v>3.2</v>
+        <v>2.85</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="Z26" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD26" t="n">
         <v>1.62</v>
       </c>
-      <c r="AA26" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AE26" t="inlineStr">
         <is>
+          <t>['4']</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG26" t="n">
-        <v>1.65</v>
+        <v>1.17</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.36</v>
+        <v>2.15</v>
       </c>
       <c r="AI26" t="n">
-        <v>2.4</v>
+        <v>1.57</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.73</v>
+        <v>3</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45616.89583333334</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,22 +3868,22 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Unión Santa Fe</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3894,83 +3894,83 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.91</v>
+        <v>3.4</v>
       </c>
       <c r="M27" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N27" t="n">
-        <v>4.33</v>
+        <v>2.25</v>
       </c>
       <c r="O27" t="n">
+        <v>4</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S27" t="n">
         <v>2.63</v>
       </c>
-      <c r="P27" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>5</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.5</v>
-      </c>
       <c r="T27" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U27" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V27" t="n">
         <v>1.06</v>
       </c>
       <c r="W27" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="X27" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="Y27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI27" t="n">
         <v>2.4</v>
       </c>
-      <c r="Z27" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>['4']</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AJ27" t="n">
-        <v>3</v>
+        <v>1.73</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45616.89583333334</v>
